--- a/dataset/Faulty/littlemem_st.xlsx
+++ b/dataset/Faulty/littlemem_st.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#define MAX_STR 10 #define MAX_STR1 10 typedef struct { int a; int b; int c; } littlemem_st_007_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_007 () { littlemem_st_007_func_001(); littlemem_st_007_func_002(1); } void littlemem_st_007_func_001 () { littlemem_st_007_s_001_gbl_str = (littlemem_st_007_s_001 *)littlemem_st_007_gbl_buf; } void littlemem_st_007_func_002 (int flag) { int i; for(i=0;i&lt;2;i++) { if(flag == MAX_STR1) { ; } else { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ } } }</t>
+          <t>#define MAX_STR 10 #define MAX_STR1 10 typedef struct { int a; int b; int c; } littlemem_st_007_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_007 () { littlemem_st_007_func_001(); littlemem_st_007_func_002(1); } void littlemem_st_007_func_002 (int flag) { int i; for(i=0;i&lt;2;i++) { if(flag == MAX_STR1) { ; } else { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ } } } void littlemem_st_007_func_001 () { littlemem_st_007_s_001_gbl_str = (littlemem_st_007_s_001 *)littlemem_st_007_gbl_buf; }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,19 +605,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>#define MAX_STR 10 #define MAX_STR2 10 #define MAX_STR3 1 typedef struct { int a; int b; int c; } littlemem_st_008_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_008 () { littlemem_st_008_func_001(); littlemem_st_008_func_002(1); } void littlemem_st_008_func_002 (int flag) { int i=0; while(i&lt;2) { if(flag == MAX_STR2) { ; } else if(flag == MAX_STR3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ } i++; } } void littlemem_st_008_func_001 () { littlemem_st_008_s_001_gbl_str = (littlemem_st_008_s_001 *)littlemem_st_008_gbl_buf; }</t>
+          <t>#define MAX_STR 10 #define MAX_STR2 10 #define MAX_STR3 1 typedef struct { int a; int b; int c; } littlemem_st_008_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_008 () { littlemem_st_008_func_001(); littlemem_st_008_func_002(1); } void littlemem_st_008_func_001 () { littlemem_st_008_s_001_gbl_str = (littlemem_st_008_s_001 *)littlemem_st_008_gbl_buf; } void littlemem_st_008_func_002 (int flag) { int i=0; while(i&lt;2) { if(flag == MAX_STR2) { ; } else if(flag == MAX_STR3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ } i++; } }</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>#define MAX_2 10 #define MAX_3 1 typedef struct { int a; int b; int c; } littlemem_st_009_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_009 () { littlemem_st_009_func_001(); littlemem_st_009_func_002(1); } void littlemem_st_009_func_001 () { littlemem_st_009_s_001_gbl_str = (littlemem_st_009_s_001 *)littlemem_st_009_gbl_buf; } void littlemem_st_009_func_002 (int flag) { int i=0; do { if(flag == MAX_2) { ; } else if(flag == MAX_3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ } i++; }while(i&lt;2); }</t>
+          <t>#define MAX_2 10 #define MAX_3 1 typedef struct { int a; int b; int c; } littlemem_st_009_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_009 () { littlemem_st_009_func_001(); littlemem_st_009_func_002(1); } void littlemem_st_009_func_002 (int flag) { int i=0; do { if(flag == MAX_2) { ; } else if(flag == MAX_3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ } i++; }while(i&lt;2); } void littlemem_st_009_func_001 () { littlemem_st_009_s_001_gbl_str = (littlemem_st_009_s_001 *)littlemem_st_009_gbl_buf; }</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>typedef struct { int a; int b; int c; } littlemem_st_010_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_010 () { littlemem_st_010_func_001(); littlemem_st_010_func_002(1); } void littlemem_st_010_func_002 (int flag) { goto label; label: littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ } void littlemem_st_010_func_001 () { littlemem_st_010_s_001_gbl_str = (littlemem_st_010_s_001 *)littlemem_st_010_gbl_buf; }</t>
+          <t>typedef struct { int a; int b; int c; } littlemem_st_010_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_010 () { littlemem_st_010_func_001(); littlemem_st_010_func_002(1); } void littlemem_st_010_func_001 () { littlemem_st_010_s_001_gbl_str = (littlemem_st_010_s_001 *)littlemem_st_010_gbl_buf; } void littlemem_st_010_func_002 (int flag) { goto label; label: littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ }</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/littlemem_st.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/littlemem_st.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>typedef struct { int a; int b; int c; } littlemem_st_011_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_011 () { littlemem_st_011_func_001(); littlemem_st_011_func_002(1); } void littlemem_st_011_func_001 () { littlemem_st_011_s_001_gbl_str = (littlemem_st_011_s_001 *)littlemem_st_011_gbl_buf; } void littlemem_st_011_func_002 (int flag) { int i=0; goto label; label: while(i&lt;2) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ i++; } }</t>
+          <t>typedef struct { int a; int b; int c; } littlemem_st_011_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[10]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[10]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[10]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[10]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[10]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[10]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[10]; extern volatile int vflag; void littlemem_st_011 () { littlemem_st_011_func_001(); littlemem_st_011_func_002(1); } void littlemem_st_011_func_002 (int flag) { int i=0; goto label; label: while(i&lt;2) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should detect this line as error*/ /*ERROR:Little Memory or Overflow*/ i++; } } void littlemem_st_011_func_001 () { littlemem_st_011_s_001_gbl_str = (littlemem_st_011_s_001 *)littlemem_st_011_gbl_buf; }</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
